--- a/Excel/QualityConfig.xlsx
+++ b/Excel/QualityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1329,7 +1329,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D5 E5:G5 H5:K5 L5 C3:C5 D3:D4 E3:E4 F3:F4 G3:G4 H3:H4 I3:I4 J3:J4 K3:K4 L3:L4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D5:L5 C3:C5 D3:L4" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/QualityConfig.xlsx
+++ b/Excel/QualityConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_id</t>
   </si>
@@ -87,6 +90,12 @@
   </si>
   <si>
     <t>CountRate</t>
+  </si>
+  <si>
+    <t>DropRate1</t>
+  </si>
+  <si>
+    <t>QualityRate1</t>
   </si>
   <si>
     <t>int</t>
@@ -1066,111 +1075,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C1:N10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="13" width="9" style="1"/>
+    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12">
+    <row r="1" spans="13:14">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="13:14">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" spans="3:14">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="3:12">
+    <row r="4" ht="13.5" spans="3:14">
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="3:12">
+    <row r="5" ht="13.5" spans="3:14">
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="3:12">
+    <row r="6" spans="3:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1198,13 +1243,19 @@
       <c r="L6" s="1">
         <v>1</v>
       </c>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="3:12">
+    <row r="7" spans="3:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>1.2</v>
@@ -1225,18 +1276,24 @@
         <v>2</v>
       </c>
       <c r="K7" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L7" s="1">
         <v>2</v>
       </c>
+      <c r="M7" s="1">
+        <v>2</v>
+      </c>
+      <c r="N7" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="3:12">
+    <row r="8" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>1.5</v>
@@ -1254,21 +1311,27 @@
         <v>10</v>
       </c>
       <c r="J8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K8" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
+      <c r="M8" s="1">
+        <v>5</v>
+      </c>
+      <c r="N8" s="1">
+        <v>20</v>
+      </c>
     </row>
-    <row r="9" spans="3:12">
+    <row r="9" spans="3:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1286,21 +1349,27 @@
         <v>20</v>
       </c>
       <c r="J9" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
       </c>
+      <c r="M9" s="1">
+        <v>10</v>
+      </c>
+      <c r="N9" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="3:12">
+    <row r="10" spans="3:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -1318,18 +1387,24 @@
         <v>200</v>
       </c>
       <c r="J10" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="L10" s="1">
         <v>5</v>
+      </c>
+      <c r="M10" s="1">
+        <v>20</v>
+      </c>
+      <c r="N10" s="1">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D5:L5 C3:C5 D3:L4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/QualityConfig.xlsx
+++ b/Excel/QualityConfig.xlsx
@@ -1238,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="1">
         <v>2</v>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
         <v>3</v>
@@ -1349,7 +1349,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1">
         <v>4</v>
@@ -1387,7 +1387,7 @@
         <v>200</v>
       </c>
       <c r="J10" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K10" s="1">
         <v>5</v>

--- a/Excel/QualityConfig.xlsx
+++ b/Excel/QualityConfig.xlsx
@@ -1387,7 +1387,7 @@
         <v>200</v>
       </c>
       <c r="J10" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1">
         <v>5</v>
